--- a/графики/Заказы 26.10 НВ (2) (1) (2) (1).xlsx
+++ b/графики/Заказы 26.10 НВ (2) (1) (2) (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41448DAE-6415-4568-B056-4551858E3982}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F255EF-1834-4E4D-8165-178BF837AD27}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="93">
   <si>
     <t>Заказ</t>
   </si>
@@ -316,6 +316,9 @@
   <si>
     <t>31 паллет / будет догруз</t>
   </si>
+  <si>
+    <t>не забрали - ОТМЕНИТЬ</t>
+  </si>
 </sst>
 </file>
 
@@ -325,7 +328,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0_ ;[Red]\-0.0\ "/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +507,15 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="39">
@@ -1230,7 +1242,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1382,6 +1394,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1409,8 +1424,9 @@
     <xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -9008,6 +9024,15 @@
           <cell r="O7567" t="str">
             <v>TSO001140837</v>
           </cell>
+          <cell r="P7567" t="str">
+            <v>ООО ЛП Тс231324-26 26.10.2026 Архипов 3976кг (Семенишин)</v>
+          </cell>
+          <cell r="Q7567">
+            <v>3976</v>
+          </cell>
+          <cell r="R7567" t="str">
+            <v>отгружен</v>
+          </cell>
         </row>
         <row r="7568">
           <cell r="O7568" t="str">
@@ -9034,478 +9059,261 @@
           <cell r="O7571" t="str">
             <v>TSO001140870</v>
           </cell>
+          <cell r="P7571" t="str">
+            <v>ООО КСК ТРЕЙД Тс229445-26 26.10.2026 Патяка 4330кг (Новожилов)</v>
+          </cell>
+          <cell r="Q7571">
+            <v>4331</v>
+          </cell>
+          <cell r="R7571" t="str">
+            <v>отгружен</v>
+          </cell>
         </row>
         <row r="7572">
           <cell r="O7572" t="str">
             <v>TSO001140852</v>
           </cell>
-          <cell r="R7572">
-            <v>2</v>
-          </cell>
-          <cell r="S7572" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7572">
-            <v>3725.2400000000002</v>
-          </cell>
-          <cell r="U7572" t="str">
-            <v>Патяка</v>
+          <cell r="P7572" t="str">
+            <v>ООО НВ Тс229523-26 26.10.2026 Патяка 3744кг (Новожилов)</v>
+          </cell>
+          <cell r="Q7572">
+            <v>3744</v>
+          </cell>
+          <cell r="R7572" t="str">
+            <v>отгружен</v>
           </cell>
         </row>
         <row r="7573">
           <cell r="O7573" t="str">
             <v>TSO001140851</v>
           </cell>
-          <cell r="R7573">
-            <v>2</v>
-          </cell>
-          <cell r="S7573" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7573">
-            <v>4396.2</v>
-          </cell>
-          <cell r="U7573" t="str">
-            <v>Мелитополь</v>
+          <cell r="P7573" t="str">
+            <v>ООО НВ Тс229522-26 26.10.2026 Мелитополь 4354кг (Новожилов)</v>
+          </cell>
+          <cell r="Q7573">
+            <v>4355</v>
+          </cell>
+          <cell r="R7573" t="str">
+            <v>отгружен</v>
           </cell>
         </row>
         <row r="7574">
           <cell r="O7574" t="str">
             <v>TSO001140853</v>
           </cell>
-          <cell r="R7574">
-            <v>2</v>
-          </cell>
-          <cell r="S7574" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7574">
-            <v>5054.7400000000016</v>
-          </cell>
-          <cell r="U7574" t="str">
-            <v>Мариуполь</v>
+          <cell r="P7574" t="str">
+            <v>ООО НВ Тс229475-26 26.10.2026 Мариуполь 5036кг (Новожилов)</v>
+          </cell>
+          <cell r="Q7574">
+            <v>5037</v>
+          </cell>
+          <cell r="R7574" t="str">
+            <v>отгружен</v>
           </cell>
         </row>
         <row r="7575">
           <cell r="O7575" t="str">
-            <v>TSO001140858</v>
-          </cell>
-          <cell r="R7575">
-            <v>1</v>
-          </cell>
-          <cell r="S7575" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7575">
-            <v>12590.420000000002</v>
-          </cell>
-          <cell r="U7575" t="str">
-            <v>Донецк</v>
+            <v>TSO001142340</v>
+          </cell>
+          <cell r="P7575" t="str">
+            <v>TSO001142348</v>
           </cell>
         </row>
         <row r="7576">
           <cell r="O7576" t="str">
-            <v>TSO001140859</v>
-          </cell>
-          <cell r="R7576">
-            <v>1</v>
-          </cell>
-          <cell r="S7576" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7576">
-            <v>5020.8</v>
-          </cell>
-          <cell r="U7576" t="str">
-            <v>Бутырин</v>
+            <v>TSO001140858</v>
           </cell>
         </row>
         <row r="7577">
           <cell r="O7577" t="str">
-            <v>TSO001140860</v>
-          </cell>
-          <cell r="R7577">
-            <v>3</v>
-          </cell>
-          <cell r="S7577" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7577">
-            <v>8925.9599999999991</v>
-          </cell>
-          <cell r="U7577" t="str">
-            <v>Бердянск</v>
+            <v>TSO001140859</v>
           </cell>
         </row>
         <row r="7578">
           <cell r="O7578" t="str">
-            <v>TSO001140871</v>
-          </cell>
-          <cell r="R7578">
-            <v>3</v>
-          </cell>
-          <cell r="S7578" t="str">
-            <v>25,10,26</v>
-          </cell>
-          <cell r="T7578">
-            <v>8807.24</v>
-          </cell>
-          <cell r="U7578" t="str">
-            <v>Мелитополь</v>
+            <v>TSO001140860</v>
           </cell>
         </row>
         <row r="7579">
           <cell r="O7579" t="str">
-            <v>TSO001141547</v>
-          </cell>
-          <cell r="P7579" t="str">
-            <v>ООО КСК ТРЕЙД Тс230168-26 25.10.2026 Крым 14771кг (Павленко)</v>
+            <v>TSO001140871</v>
           </cell>
         </row>
         <row r="7580">
           <cell r="O7580" t="str">
-            <v>TSO001141537</v>
+            <v>TSO001142464</v>
           </cell>
         </row>
         <row r="7581">
           <cell r="O7581" t="str">
-            <v>TSO001141496</v>
+            <v>TSO001141547</v>
+          </cell>
+          <cell r="P7581" t="str">
+            <v>ООО КСК ТРЕЙД Тс230168-26 25.10.2026 Крым 14771кг (Павленко)</v>
           </cell>
         </row>
         <row r="7582">
           <cell r="O7582" t="str">
-            <v>TSO001141499</v>
+            <v>TSO001141537</v>
           </cell>
         </row>
         <row r="7583">
           <cell r="O7583" t="str">
-            <v>TSO001141585</v>
+            <v>TSO001141496</v>
+          </cell>
+          <cell r="P7583" t="str">
+            <v>ООО КСК ТРЕЙД Тс230467-26 26.10.2026 Крым 15336кг (Кокшин)</v>
+          </cell>
+          <cell r="Q7583">
+            <v>15337</v>
+          </cell>
+          <cell r="R7583" t="str">
+            <v>отгружен</v>
           </cell>
         </row>
         <row r="7584">
           <cell r="O7584" t="str">
-            <v>TSO001141577</v>
-          </cell>
-          <cell r="P7584">
-            <v>2964.22</v>
+            <v>TSO001141499</v>
+          </cell>
+          <cell r="P7584" t="str">
+            <v>ООО КСК ТРЕЙД Тс230409-26 26.10.2026 Вердиева 2342кг (Кокшин)</v>
           </cell>
           <cell r="Q7584">
-            <v>0</v>
-          </cell>
-          <cell r="R7584">
-            <v>6</v>
-          </cell>
-          <cell r="S7584" t="str">
-            <v>26,10,26</v>
-          </cell>
-          <cell r="T7584">
-            <v>2964.2200000000003</v>
-          </cell>
-          <cell r="U7584" t="str">
-            <v>Бердянск</v>
+            <v>2342</v>
+          </cell>
+          <cell r="R7584" t="str">
+            <v>отгружен</v>
           </cell>
         </row>
         <row r="7585">
           <cell r="O7585" t="str">
-            <v>TSO001141576</v>
-          </cell>
-          <cell r="P7585">
-            <v>5646.58</v>
-          </cell>
-          <cell r="Q7585">
-            <v>-273</v>
-          </cell>
-          <cell r="R7585">
-            <v>6</v>
-          </cell>
-          <cell r="S7585" t="str">
-            <v>26,10,26</v>
-          </cell>
-          <cell r="T7585">
-            <v>5919.58</v>
-          </cell>
-          <cell r="U7585" t="str">
-            <v>Мелитополь</v>
+            <v>TSO001141585</v>
           </cell>
         </row>
         <row r="7586">
           <cell r="O7586" t="str">
-            <v>+</v>
-          </cell>
-          <cell r="R7586">
-            <v>6</v>
-          </cell>
-          <cell r="S7586" t="str">
-            <v>26,10,26</v>
-          </cell>
-          <cell r="T7586">
-            <v>1920</v>
-          </cell>
-          <cell r="U7586" t="str">
-            <v>Мелитополь</v>
+            <v>TSO001141577</v>
           </cell>
         </row>
         <row r="7587">
           <cell r="O7587" t="str">
-            <v>TSO001141584</v>
-          </cell>
-          <cell r="P7587">
-            <v>16677.73</v>
-          </cell>
-          <cell r="Q7587">
-            <v>0</v>
-          </cell>
-          <cell r="R7587">
-            <v>4</v>
-          </cell>
-          <cell r="S7587" t="str">
-            <v>26,10,26</v>
-          </cell>
-          <cell r="T7587">
-            <v>16677.73</v>
-          </cell>
-          <cell r="U7587" t="str">
-            <v>Донецк</v>
+            <v>TSO001141576</v>
           </cell>
         </row>
         <row r="7588">
           <cell r="O7588" t="str">
-            <v>TSO001141581</v>
-          </cell>
-          <cell r="R7588">
-            <v>4</v>
-          </cell>
-          <cell r="S7588" t="str">
-            <v>26,10,26</v>
-          </cell>
-          <cell r="T7588">
-            <v>1998.1400000000003</v>
-          </cell>
-          <cell r="U7588" t="str">
-            <v>Мариуполь</v>
+            <v>TSO001142329</v>
           </cell>
         </row>
         <row r="7589">
           <cell r="O7589" t="str">
-            <v>TSO001141596</v>
-          </cell>
-          <cell r="P7589">
-            <v>17075.75</v>
-          </cell>
-          <cell r="Q7589">
-            <v>-303.5</v>
-          </cell>
-          <cell r="R7589">
-            <v>5</v>
-          </cell>
-          <cell r="S7589" t="str">
-            <v>26,10,26</v>
-          </cell>
-          <cell r="T7589">
-            <v>17379.25</v>
-          </cell>
-          <cell r="U7589" t="str">
-            <v>Луганск</v>
+            <v>TSO001142285</v>
           </cell>
         </row>
         <row r="7590">
           <cell r="O7590" t="str">
-            <v>TSO001141671</v>
-          </cell>
-          <cell r="P7590">
-            <v>1543.48</v>
-          </cell>
-          <cell r="Q7590">
-            <v>0</v>
+            <v>TSO001141584</v>
           </cell>
         </row>
         <row r="7591">
           <cell r="O7591" t="str">
-            <v>TSO001141667</v>
-          </cell>
-          <cell r="P7591">
-            <v>7117.68</v>
-          </cell>
-          <cell r="Q7591">
-            <v>0</v>
+            <v>TSO001141581</v>
           </cell>
         </row>
         <row r="7592">
           <cell r="O7592" t="str">
-            <v>TSO001141676</v>
-          </cell>
-          <cell r="P7592">
-            <v>6229.5</v>
+            <v>TSO001141596</v>
           </cell>
           <cell r="Q7592">
-            <v>-6.0000000001309672E-2</v>
+            <v>17109</v>
+          </cell>
+          <cell r="R7592" t="str">
+            <v>отгружен</v>
           </cell>
         </row>
         <row r="7593">
           <cell r="O7593" t="str">
-            <v>TSO001141680</v>
+            <v>TSO001142330</v>
           </cell>
         </row>
         <row r="7594">
           <cell r="O7594" t="str">
-            <v>TSO001141507</v>
+            <v>TSO001141671</v>
           </cell>
         </row>
         <row r="7595">
           <cell r="O7595" t="str">
-            <v>TSO001141572</v>
+            <v>TSO001141667</v>
           </cell>
         </row>
         <row r="7596">
           <cell r="O7596" t="str">
-            <v>TSO001141619</v>
+            <v>TSO001141676</v>
           </cell>
         </row>
         <row r="7597">
           <cell r="O7597" t="str">
-            <v>TSO001141618</v>
-          </cell>
-          <cell r="P7597">
-            <v>11337.57</v>
-          </cell>
-          <cell r="Q7597">
-            <v>0</v>
-          </cell>
-          <cell r="R7597">
-            <v>7</v>
-          </cell>
-          <cell r="S7597" t="str">
-            <v>27,10,26</v>
-          </cell>
-          <cell r="T7597">
-            <v>11337.57</v>
-          </cell>
-          <cell r="U7597" t="str">
-            <v>Донецк</v>
+            <v>TSO001141680</v>
           </cell>
         </row>
         <row r="7598">
           <cell r="O7598" t="str">
-            <v>TSO001141631</v>
-          </cell>
-          <cell r="P7598">
-            <v>5063.2</v>
-          </cell>
-          <cell r="Q7598">
-            <v>0</v>
-          </cell>
-          <cell r="R7598">
-            <v>8</v>
-          </cell>
-          <cell r="S7598" t="str">
-            <v>27,10,26</v>
-          </cell>
-          <cell r="T7598">
-            <v>5063.2</v>
-          </cell>
-          <cell r="U7598" t="str">
-            <v>Горняк</v>
+            <v>TSO001141507</v>
           </cell>
         </row>
         <row r="7599">
           <cell r="O7599" t="str">
-            <v>TSO001141626</v>
-          </cell>
-          <cell r="P7599">
-            <v>12699.64</v>
-          </cell>
-          <cell r="Q7599">
-            <v>0</v>
-          </cell>
-          <cell r="R7599">
-            <v>8</v>
-          </cell>
-          <cell r="S7599" t="str">
-            <v>27,10,26</v>
-          </cell>
-          <cell r="T7599">
-            <v>12699.64</v>
-          </cell>
-          <cell r="U7599" t="str">
-            <v>Луганск</v>
+            <v>TSO001141572</v>
           </cell>
         </row>
         <row r="7600">
           <cell r="O7600" t="str">
-            <v>TSO001141623</v>
+            <v>TSO001141619</v>
           </cell>
         </row>
         <row r="7601">
           <cell r="O7601" t="str">
-            <v>TSO001141614</v>
-          </cell>
-          <cell r="P7601">
-            <v>4495.2</v>
-          </cell>
-          <cell r="Q7601">
-            <v>0</v>
-          </cell>
-          <cell r="R7601">
-            <v>9</v>
-          </cell>
-          <cell r="S7601" t="str">
-            <v>27,10,26</v>
-          </cell>
-          <cell r="T7601">
-            <v>4495.2</v>
-          </cell>
-          <cell r="U7601" t="str">
-            <v>Убийконь</v>
+            <v>TSO001141618</v>
           </cell>
         </row>
         <row r="7602">
           <cell r="O7602" t="str">
-            <v>TSO001141615</v>
-          </cell>
-          <cell r="P7602">
-            <v>1012.8</v>
-          </cell>
-          <cell r="Q7602">
-            <v>0</v>
-          </cell>
-          <cell r="R7602">
-            <v>9</v>
-          </cell>
-          <cell r="S7602" t="str">
-            <v>27,10,26</v>
-          </cell>
-          <cell r="T7602">
-            <v>1012.8000000000001</v>
-          </cell>
-          <cell r="U7602" t="str">
-            <v>Мелитополь</v>
+            <v>TSO001141631</v>
           </cell>
         </row>
         <row r="7603">
           <cell r="O7603" t="str">
-            <v>TSO001141714</v>
+            <v>TSO001141626</v>
           </cell>
         </row>
         <row r="7604">
           <cell r="O7604" t="str">
-            <v>TSO001141681</v>
-          </cell>
-          <cell r="P7604">
-            <v>12427.88</v>
-          </cell>
-          <cell r="Q7604">
-            <v>0</v>
+            <v>TSO001141623</v>
           </cell>
         </row>
         <row r="7605">
           <cell r="O7605" t="str">
+            <v>TSO001141614</v>
+          </cell>
+        </row>
+        <row r="7606">
+          <cell r="O7606" t="str">
+            <v>TSO001141615</v>
+          </cell>
+        </row>
+        <row r="7607">
+          <cell r="O7607" t="str">
+            <v>TSO001141714</v>
+          </cell>
+        </row>
+        <row r="7608">
+          <cell r="O7608" t="str">
+            <v>TSO001141681</v>
+          </cell>
+        </row>
+        <row r="7609">
+          <cell r="O7609" t="str">
             <v>TSO001141686</v>
-          </cell>
-          <cell r="P7605">
-            <v>12988.24</v>
-          </cell>
-          <cell r="Q7605">
-            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -10185,21 +9993,21 @@
       <c r="M2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="N2" s="45" t="str">
+      <c r="N2" s="45">
         <f>VLOOKUP(B2,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O2" s="45">
         <f>VLOOKUP(B2,[1]Лист1!$O:$T,6,0)</f>
-        <v>5020.8</v>
+        <v>0</v>
       </c>
       <c r="P2" s="46">
         <f>D2-O2</f>
-        <v>0</v>
+        <v>5020.8</v>
       </c>
       <c r="Q2" s="47">
         <f>VLOOKUP(B2,[1]Лист1!$O:$R,4,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10239,32 +10047,32 @@
       <c r="L3" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="52" t="str">
+      <c r="M3" s="52">
         <f>VLOOKUP(B3,[1]Лист1!$O:$U,7,0)</f>
-        <v>Донецк</v>
-      </c>
-      <c r="N3" s="52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N3" s="52">
         <f>VLOOKUP(B3,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O3" s="52">
         <f>VLOOKUP(B3,[1]Лист1!$O:$T,6,0)</f>
-        <v>12590.420000000002</v>
+        <v>0</v>
       </c>
       <c r="P3" s="53">
         <f>D3-O3</f>
-        <v>0</v>
+        <v>12590.42</v>
       </c>
       <c r="Q3" s="54">
         <f>VLOOKUP(B3,[1]Лист1!$O:$R,4,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="92"/>
+      <c r="B4" s="93"/>
       <c r="C4" s="55"/>
       <c r="D4" s="55">
         <f>SUM(D2:D3)</f>
@@ -10345,25 +10153,25 @@
       <c r="L6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="59" t="str">
+      <c r="M6" s="59">
         <f>VLOOKUP(B6,[1]Лист1!$O:$U,7,0)</f>
-        <v>Мариуполь</v>
-      </c>
-      <c r="N6" s="59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N6" s="59">
         <f>VLOOKUP(B6,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O6" s="59">
         <f>VLOOKUP(B6,[1]Лист1!$O:$T,6,0)</f>
-        <v>5054.7400000000016</v>
+        <v>0</v>
       </c>
       <c r="P6" s="60">
         <f>D6-O6</f>
-        <v>-52.500000000001819</v>
-      </c>
-      <c r="Q6" s="61">
+        <v>5002.24</v>
+      </c>
+      <c r="Q6" s="61" t="str">
         <f>VLOOKUP(B6,[1]Лист1!$O:$R,4,0)</f>
-        <v>2</v>
+        <v>отгружен</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -10403,25 +10211,25 @@
       <c r="L7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="59" t="str">
+      <c r="M7" s="59">
         <f>VLOOKUP(B7,[1]Лист1!$O:$U,7,0)</f>
-        <v>Мелитополь</v>
-      </c>
-      <c r="N7" s="59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N7" s="59">
         <f>VLOOKUP(B7,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O7" s="59">
         <f>VLOOKUP(B7,[1]Лист1!$O:$T,6,0)</f>
-        <v>4396.2</v>
+        <v>0</v>
       </c>
       <c r="P7" s="60">
         <f>D7-O7</f>
-        <v>-66.5</v>
-      </c>
-      <c r="Q7" s="61">
+        <v>4329.7</v>
+      </c>
+      <c r="Q7" s="61" t="str">
         <f>VLOOKUP(B7,[1]Лист1!$O:$R,4,0)</f>
-        <v>2</v>
+        <v>отгружен</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -10464,21 +10272,21 @@
       <c r="M8" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="59" t="str">
+      <c r="N8" s="59">
         <f>VLOOKUP(B8,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O8" s="59">
         <f>VLOOKUP(B8,[1]Лист1!$O:$T,6,0)</f>
-        <v>3725.2400000000002</v>
+        <v>0</v>
       </c>
       <c r="P8" s="60">
         <f>D8-O8</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="61">
+        <v>3725.24</v>
+      </c>
+      <c r="Q8" s="61" t="str">
         <f>VLOOKUP(B8,[1]Лист1!$O:$R,4,0)</f>
-        <v>2</v>
+        <v>отгружен</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10508,12 +10316,15 @@
       <c r="R9" s="36" t="s">
         <v>86</v>
       </c>
+      <c r="S9" s="101" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="92"/>
+      <c r="B10" s="93"/>
       <c r="C10" s="55"/>
       <c r="D10" s="55">
         <f>SUM(D5:D9)</f>
@@ -10529,7 +10340,7 @@
       <c r="L10" s="55"/>
       <c r="P10" s="81">
         <f>SUM(P5:P8)</f>
-        <v>-119.00000000000182</v>
+        <v>13057.179999999998</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -10569,25 +10380,25 @@
       <c r="L11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="45" t="str">
+      <c r="M11" s="45">
         <f>VLOOKUP(B11,[1]Лист1!$O:$U,7,0)</f>
-        <v>Мелитополь</v>
-      </c>
-      <c r="N11" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="N11" s="45">
         <f>VLOOKUP(B11,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O11" s="45">
         <f>VLOOKUP(B11,[1]Лист1!$O:$T,6,0)</f>
-        <v>8807.24</v>
+        <v>0</v>
       </c>
       <c r="P11" s="46">
         <f t="shared" ref="P11:P12" si="0">D11-O11</f>
-        <v>-350</v>
+        <v>8457.24</v>
       </c>
       <c r="Q11" s="47">
         <f>VLOOKUP(B11,[1]Лист1!$O:$R,4,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -10627,25 +10438,25 @@
       <c r="L12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="59" t="str">
+      <c r="M12" s="59">
         <f>VLOOKUP(B12,[1]Лист1!$O:$U,7,0)</f>
-        <v>Бердянск</v>
-      </c>
-      <c r="N12" s="59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N12" s="59">
         <f>VLOOKUP(B12,[1]Лист1!$O:$S,5,0)</f>
-        <v>25,10,26</v>
+        <v>0</v>
       </c>
       <c r="O12" s="59">
         <f>VLOOKUP(B12,[1]Лист1!$O:$T,6,0)</f>
-        <v>8925.9599999999991</v>
+        <v>0</v>
       </c>
       <c r="P12" s="60">
         <f t="shared" si="0"/>
-        <v>-140</v>
+        <v>8785.9599999999991</v>
       </c>
       <c r="Q12" s="61">
         <f>VLOOKUP(B12,[1]Лист1!$O:$R,4,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10679,10 +10490,10 @@
       </c>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="92"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="55"/>
       <c r="D14" s="55">
         <f>SUM(D11:D13)</f>
@@ -10698,7 +10509,7 @@
       <c r="L14" s="55"/>
       <c r="P14" s="82">
         <f>SUM(P11:P12)</f>
-        <v>-490</v>
+        <v>17243.199999999997</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -10739,30 +10550,30 @@
       <c r="L15" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="66" t="str">
+      <c r="M15" s="66">
         <f>VLOOKUP(B15,[1]Лист1!$O:$U,7,0)</f>
-        <v>Донецк</v>
-      </c>
-      <c r="N15" s="66" t="str">
+        <v>0</v>
+      </c>
+      <c r="N15" s="66">
         <f>VLOOKUP(B15,[1]Лист1!$O:$S,5,0)</f>
-        <v>26,10,26</v>
+        <v>0</v>
       </c>
       <c r="O15" s="66">
         <f>VLOOKUP(B15,[1]Лист1!$O:$T,6,0)-1900</f>
-        <v>14777.73</v>
+        <v>-1900</v>
       </c>
       <c r="P15" s="67">
         <f>D15-O15</f>
-        <v>0</v>
+        <v>16677.73</v>
       </c>
       <c r="Q15" s="68">
         <f>VLOOKUP(B15,[1]Лист1!$O:$R,4,0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="S15" s="100" t="s">
+      <c r="S15" s="91" t="s">
         <v>90</v>
       </c>
     </row>
@@ -10803,33 +10614,33 @@
       <c r="L16" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="52" t="str">
+      <c r="M16" s="52">
         <f>VLOOKUP(B16,[1]Лист1!$O:$U,7,0)</f>
-        <v>Мариуполь</v>
-      </c>
-      <c r="N16" s="52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N16" s="52">
         <f>VLOOKUP(B16,[1]Лист1!$O:$S,5,0)</f>
-        <v>26,10,26</v>
+        <v>0</v>
       </c>
       <c r="O16" s="52">
         <f>VLOOKUP(B16,[1]Лист1!$O:$T,6,0)</f>
-        <v>1998.1400000000003</v>
+        <v>0</v>
       </c>
       <c r="P16" s="53">
         <f>D16-O16</f>
-        <v>0</v>
+        <v>1998.14</v>
       </c>
       <c r="Q16" s="54">
         <f>VLOOKUP(B16,[1]Лист1!$O:$R,4,0)</f>
-        <v>4</v>
-      </c>
-      <c r="S16" s="100"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="91"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="92"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="69"/>
       <c r="D17" s="69">
         <f>SUM(D15:D16)</f>
@@ -10881,27 +10692,27 @@
       <c r="L18" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="45" t="str">
+      <c r="M18" s="45">
         <f>VLOOKUP(B18,[1]Лист1!$O:$U,7,0)</f>
-        <v>Луганск</v>
-      </c>
-      <c r="N18" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="N18" s="45">
         <f>VLOOKUP(B18,[1]Лист1!$O:$S,5,0)</f>
-        <v>26,10,26</v>
+        <v>0</v>
       </c>
       <c r="O18" s="45">
         <f>VLOOKUP(B18,[1]Лист1!$O:$T,6,0)</f>
-        <v>17379.25</v>
+        <v>0</v>
       </c>
       <c r="P18" s="46">
         <f>D18-O18</f>
-        <v>-303.5</v>
-      </c>
-      <c r="Q18" s="47">
+        <v>17075.75</v>
+      </c>
+      <c r="Q18" s="47" t="str">
         <f>VLOOKUP(B18,[1]Лист1!$O:$R,4,0)</f>
-        <v>5</v>
-      </c>
-      <c r="S18" s="100" t="s">
+        <v>отгружен</v>
+      </c>
+      <c r="S18" s="102" t="s">
         <v>91</v>
       </c>
     </row>
@@ -10932,13 +10743,15 @@
       <c r="R19" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="S19" s="100"/>
+      <c r="S19" s="101" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="91" t="s">
+      <c r="A20" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="92"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="55"/>
       <c r="D20" s="55">
         <f>SUM(D18)</f>
@@ -10954,7 +10767,7 @@
       <c r="L20" s="55"/>
       <c r="P20" s="81">
         <f>SUM(P18)</f>
-        <v>-303.5</v>
+        <v>17075.75</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -11023,25 +10836,25 @@
       <c r="L22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="59" t="str">
+      <c r="M22" s="59">
         <f>VLOOKUP(B22,[1]Лист1!$O:$U,7,0)</f>
-        <v>Бердянск</v>
-      </c>
-      <c r="N22" s="59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N22" s="59">
         <f>VLOOKUP(B22,[1]Лист1!$O:$S,5,0)</f>
-        <v>26,10,26</v>
+        <v>0</v>
       </c>
       <c r="O22" s="59">
         <f>VLOOKUP(B22,[1]Лист1!$O:$T,6,0)</f>
-        <v>2964.2200000000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="60">
         <f t="shared" ref="P22" si="1">D22-O22</f>
-        <v>-42.000000000000455</v>
+        <v>2922.22</v>
       </c>
       <c r="Q22" s="61">
         <f>VLOOKUP(B22,[1]Лист1!$O:$R,4,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -11109,25 +10922,25 @@
       <c r="L24" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="59" t="str">
+      <c r="M24" s="59">
         <f>VLOOKUP(B24,[1]Лист1!$O:$U,7,0)</f>
-        <v>Мелитополь</v>
-      </c>
-      <c r="N24" s="59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N24" s="59">
         <f>VLOOKUP(B24,[1]Лист1!$O:$S,5,0)</f>
-        <v>26,10,26</v>
+        <v>0</v>
       </c>
       <c r="O24" s="59">
         <f>VLOOKUP(B24,[1]Лист1!$O:$T,6,0)</f>
-        <v>5919.58</v>
+        <v>0</v>
       </c>
       <c r="P24" s="60">
         <f>D24-O24</f>
-        <v>-273</v>
+        <v>5646.58</v>
       </c>
       <c r="Q24" s="61">
         <f>VLOOKUP(B24,[1]Лист1!$O:$R,4,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11163,10 +10976,10 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="92"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55">
         <f>SUM(D21:D25)</f>
@@ -11182,7 +10995,7 @@
       <c r="L26" s="55"/>
       <c r="P26" s="82">
         <f>SUM(P21:P25)</f>
-        <v>-315.00000000000045</v>
+        <v>8568.7999999999993</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -11251,32 +11064,32 @@
       <c r="L28" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="M28" s="52" t="str">
+      <c r="M28" s="52">
         <f>VLOOKUP(B28,[1]Лист1!$O:$U,7,0)</f>
-        <v>Донецк</v>
-      </c>
-      <c r="N28" s="52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N28" s="52">
         <f>VLOOKUP(B28,[1]Лист1!$O:$S,5,0)</f>
-        <v>27,10,26</v>
+        <v>0</v>
       </c>
       <c r="O28" s="52">
         <f>VLOOKUP(B28,[1]Лист1!$O:$T,6,0)</f>
-        <v>11337.57</v>
+        <v>0</v>
       </c>
       <c r="P28" s="53">
         <f>D28-O28</f>
-        <v>0</v>
+        <v>11337.57</v>
       </c>
       <c r="Q28" s="54">
         <f>VLOOKUP(B28,[1]Лист1!$O:$R,4,0)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="94"/>
+      <c r="B29" s="95"/>
       <c r="C29" s="55"/>
       <c r="D29" s="55">
         <f>SUM(D27:D28)</f>
@@ -11328,25 +11141,25 @@
       <c r="L30" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="M30" s="45" t="str">
+      <c r="M30" s="45">
         <f>VLOOKUP(B30,[1]Лист1!$O:$U,7,0)</f>
-        <v>Луганск</v>
-      </c>
-      <c r="N30" s="45" t="str">
+        <v>0</v>
+      </c>
+      <c r="N30" s="45">
         <f>VLOOKUP(B30,[1]Лист1!$O:$S,5,0)</f>
-        <v>27,10,26</v>
+        <v>0</v>
       </c>
       <c r="O30" s="45">
         <f>VLOOKUP(B30,[1]Лист1!$O:$T,6,0)</f>
-        <v>12699.64</v>
+        <v>0</v>
       </c>
       <c r="P30" s="46">
         <f t="shared" ref="P30:P31" si="2">D30-O30</f>
-        <v>0</v>
+        <v>12699.64</v>
       </c>
       <c r="Q30" s="47">
         <f>VLOOKUP(B30,[1]Лист1!$O:$R,4,0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11389,28 +11202,28 @@
       <c r="M31" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="N31" s="52" t="str">
+      <c r="N31" s="52">
         <f>VLOOKUP(B31,[1]Лист1!$O:$S,5,0)</f>
-        <v>27,10,26</v>
+        <v>0</v>
       </c>
       <c r="O31" s="52">
         <f>VLOOKUP(B31,[1]Лист1!$O:$T,6,0)</f>
-        <v>5063.2</v>
+        <v>0</v>
       </c>
       <c r="P31" s="53">
         <f t="shared" si="2"/>
-        <v>-72</v>
+        <v>4991.2</v>
       </c>
       <c r="Q31" s="54">
         <f>VLOOKUP(B31,[1]Лист1!$O:$R,4,0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="94" t="s">
+      <c r="A32" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="94"/>
+      <c r="B32" s="95"/>
       <c r="C32" s="55"/>
       <c r="D32" s="55">
         <f>SUM(D30:D31)</f>
@@ -11426,7 +11239,7 @@
       <c r="L32" s="55"/>
       <c r="P32" s="55">
         <f>SUM(P30:P31)</f>
-        <v>-72</v>
+        <v>17690.84</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -11498,21 +11311,21 @@
       <c r="M34" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="N34" s="59" t="str">
+      <c r="N34" s="59">
         <f>VLOOKUP(B34,[1]Лист1!$O:$S,5,0)</f>
-        <v>27,10,26</v>
+        <v>0</v>
       </c>
       <c r="O34" s="59">
         <f>VLOOKUP(B34,[1]Лист1!$O:$T,6,0)</f>
-        <v>4495.2</v>
+        <v>0</v>
       </c>
       <c r="P34" s="60">
         <f t="shared" ref="P34:P35" si="3">D34-O34</f>
-        <v>0</v>
+        <v>4495.2</v>
       </c>
       <c r="Q34" s="61">
         <f>VLOOKUP(B34,[1]Лист1!$O:$R,4,0)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11552,32 +11365,32 @@
       <c r="L35" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="M35" s="52" t="str">
+      <c r="M35" s="52">
         <f>VLOOKUP(B35,[1]Лист1!$O:$U,7,0)</f>
-        <v>Мелитополь</v>
-      </c>
-      <c r="N35" s="52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N35" s="52">
         <f>VLOOKUP(B35,[1]Лист1!$O:$S,5,0)</f>
-        <v>27,10,26</v>
+        <v>0</v>
       </c>
       <c r="O35" s="52">
         <f>VLOOKUP(B35,[1]Лист1!$O:$T,6,0)</f>
-        <v>1012.8000000000001</v>
+        <v>0</v>
       </c>
       <c r="P35" s="53">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1012.8</v>
       </c>
       <c r="Q35" s="54">
         <f>VLOOKUP(B35,[1]Лист1!$O:$R,4,0)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="93" t="s">
+      <c r="A36" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="93"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="79"/>
       <c r="D36" s="79">
         <f>SUM(D33:D35)</f>
@@ -11598,18 +11411,17 @@
       <sortCondition ref="H1"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="11">
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+  <mergeCells count="10">
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="13" priority="16"/>
@@ -11668,7 +11480,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="95"/>
+      <c r="A1" s="96"/>
       <c r="B1" s="11" t="s">
         <v>22</v>
       </c>
@@ -11702,7 +11514,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="95"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="11" t="s">
         <v>17</v>
       </c>
@@ -11726,7 +11538,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="96"/>
+      <c r="A3" s="97"/>
       <c r="B3" s="15" t="s">
         <v>16</v>
       </c>
@@ -11832,7 +11644,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="97">
+      <c r="A6" s="98">
         <v>7</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -11868,7 +11680,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="18" t="s">
         <v>17</v>
       </c>
@@ -11902,7 +11714,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
+      <c r="A8" s="99"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
@@ -11970,7 +11782,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="99">
+      <c r="A10" s="100">
         <v>12</v>
       </c>
       <c r="B10" s="21" t="s">
@@ -12006,7 +11818,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="96"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="15" t="s">
         <v>19</v>
       </c>
@@ -12040,7 +11852,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="97"/>
+      <c r="A12" s="98"/>
       <c r="B12" s="18" t="s">
         <v>17</v>
       </c>
@@ -12074,7 +11886,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="98"/>
+      <c r="A13" s="99"/>
       <c r="B13" s="4" t="s">
         <v>17</v>
       </c>
